--- a/results/supplement/Figure_2_data_meta_1_heterogeneity_0_pet_peese.xlsx
+++ b/results/supplement/Figure_2_data_meta_1_heterogeneity_0_pet_peese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <si>
     <t xml:space="preserve">cID</t>
   </si>
@@ -1710,9 +1710,6 @@
   </si>
   <si>
     <t xml:space="preserve">439-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">439-3</t>
   </si>
   <si>
     <t xml:space="preserve">439-4</t>
@@ -10362,18 +10359,22 @@
       <c r="A564" t="s">
         <v>566</v>
       </c>
-      <c r="B564"/>
-      <c r="C564" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="D564"/>
+      <c r="B564" t="n">
+        <v>8.74741415078963</v>
+      </c>
+      <c r="C564" t="n">
+        <v>0</v>
+      </c>
+      <c r="D564" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
         <v>567</v>
       </c>
       <c r="B565" t="n">
-        <v>8.74741415078963</v>
+        <v>8.72641119268489</v>
       </c>
       <c r="C565" t="n">
         <v>0</v>
@@ -10387,7 +10388,7 @@
         <v>568</v>
       </c>
       <c r="B566" t="n">
-        <v>8.72641119268489</v>
+        <v>5.17734374007013</v>
       </c>
       <c r="C566" t="n">
         <v>0</v>
@@ -10401,7 +10402,7 @@
         <v>569</v>
       </c>
       <c r="B567" t="n">
-        <v>5.17734374007013</v>
+        <v>5.00053524017336</v>
       </c>
       <c r="C567" t="n">
         <v>0</v>
@@ -10415,7 +10416,7 @@
         <v>570</v>
       </c>
       <c r="B568" t="n">
-        <v>5.00053524017336</v>
+        <v>5.0848230224641</v>
       </c>
       <c r="C568" t="n">
         <v>0</v>
@@ -10429,7 +10430,7 @@
         <v>571</v>
       </c>
       <c r="B569" t="n">
-        <v>5.0848230224641</v>
+        <v>17.3582502430768</v>
       </c>
       <c r="C569" t="n">
         <v>0</v>
@@ -10443,10 +10444,10 @@
         <v>572</v>
       </c>
       <c r="B570" t="n">
-        <v>17.3582502430768</v>
+        <v>60.8955567158538</v>
       </c>
       <c r="C570" t="n">
-        <v>0</v>
+        <v>36.3636363636364</v>
       </c>
       <c r="D570" t="b">
         <v>0</v>
@@ -10457,10 +10458,10 @@
         <v>573</v>
       </c>
       <c r="B571" t="n">
-        <v>60.8955567158538</v>
+        <v>23.7858424554834</v>
       </c>
       <c r="C571" t="n">
-        <v>36.3636363636364</v>
+        <v>8.33333333333333</v>
       </c>
       <c r="D571" t="b">
         <v>0</v>
@@ -10471,10 +10472,10 @@
         <v>574</v>
       </c>
       <c r="B572" t="n">
-        <v>23.7858424554834</v>
+        <v>5.89178320953848</v>
       </c>
       <c r="C572" t="n">
-        <v>8.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="D572" t="b">
         <v>0</v>
@@ -10485,10 +10486,10 @@
         <v>575</v>
       </c>
       <c r="B573" t="n">
-        <v>5.89178320953848</v>
+        <v>10.1799687605084</v>
       </c>
       <c r="C573" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="D573" t="b">
         <v>0</v>
@@ -10499,10 +10500,10 @@
         <v>576</v>
       </c>
       <c r="B574" t="n">
-        <v>10.1799687605084</v>
+        <v>7.25301644569935</v>
       </c>
       <c r="C574" t="n">
-        <v>16.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="D574" t="b">
         <v>0</v>
@@ -10513,10 +10514,10 @@
         <v>577</v>
       </c>
       <c r="B575" t="n">
-        <v>7.25301644569935</v>
+        <v>35.4135548314448</v>
       </c>
       <c r="C575" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="D575" t="b">
         <v>0</v>
@@ -10527,10 +10528,10 @@
         <v>578</v>
       </c>
       <c r="B576" t="n">
-        <v>35.4135548314448</v>
+        <v>65.049931185619</v>
       </c>
       <c r="C576" t="n">
-        <v>16.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="D576" t="b">
         <v>0</v>
@@ -10541,10 +10542,10 @@
         <v>579</v>
       </c>
       <c r="B577" t="n">
-        <v>65.049931185619</v>
+        <v>15.4774783898371</v>
       </c>
       <c r="C577" t="n">
-        <v>50</v>
+        <v>14.2857142857143</v>
       </c>
       <c r="D577" t="b">
         <v>0</v>
@@ -10555,10 +10556,10 @@
         <v>580</v>
       </c>
       <c r="B578" t="n">
-        <v>15.4774783898371</v>
+        <v>60.9555505512924</v>
       </c>
       <c r="C578" t="n">
-        <v>14.2857142857143</v>
+        <v>28.5714285714286</v>
       </c>
       <c r="D578" t="b">
         <v>0</v>
@@ -10569,10 +10570,10 @@
         <v>581</v>
       </c>
       <c r="B579" t="n">
-        <v>60.9555505512924</v>
+        <v>33.6299644603053</v>
       </c>
       <c r="C579" t="n">
-        <v>28.5714285714286</v>
+        <v>0</v>
       </c>
       <c r="D579" t="b">
         <v>0</v>
@@ -10583,7 +10584,7 @@
         <v>582</v>
       </c>
       <c r="B580" t="n">
-        <v>33.6299644603053</v>
+        <v>6.07425348070183</v>
       </c>
       <c r="C580" t="n">
         <v>0</v>
@@ -10597,7 +10598,7 @@
         <v>583</v>
       </c>
       <c r="B581" t="n">
-        <v>6.07425348070183</v>
+        <v>9.64851004251558</v>
       </c>
       <c r="C581" t="n">
         <v>0</v>
@@ -10611,7 +10612,7 @@
         <v>584</v>
       </c>
       <c r="B582" t="n">
-        <v>9.64851004251558</v>
+        <v>5.00269264201911</v>
       </c>
       <c r="C582" t="n">
         <v>0</v>
@@ -10625,7 +10626,7 @@
         <v>585</v>
       </c>
       <c r="B583" t="n">
-        <v>5.00269264201911</v>
+        <v>6.199729090947</v>
       </c>
       <c r="C583" t="n">
         <v>0</v>
@@ -10639,7 +10640,7 @@
         <v>586</v>
       </c>
       <c r="B584" t="n">
-        <v>6.199729090947</v>
+        <v>5.02904938680756</v>
       </c>
       <c r="C584" t="n">
         <v>0</v>
@@ -10653,7 +10654,7 @@
         <v>587</v>
       </c>
       <c r="B585" t="n">
-        <v>5.02904938680756</v>
+        <v>5.33382938381277</v>
       </c>
       <c r="C585" t="n">
         <v>0</v>
@@ -10667,7 +10668,7 @@
         <v>588</v>
       </c>
       <c r="B586" t="n">
-        <v>5.33382938381277</v>
+        <v>9.27435340575821</v>
       </c>
       <c r="C586" t="n">
         <v>0</v>
@@ -10681,10 +10682,10 @@
         <v>589</v>
       </c>
       <c r="B587" t="n">
-        <v>9.27435340575821</v>
+        <v>8.21526479017738</v>
       </c>
       <c r="C587" t="n">
-        <v>0</v>
+        <v>1.3840830449827</v>
       </c>
       <c r="D587" t="b">
         <v>0</v>
@@ -10695,10 +10696,10 @@
         <v>590</v>
       </c>
       <c r="B588" t="n">
-        <v>8.21526479017738</v>
+        <v>20.611365319001</v>
       </c>
       <c r="C588" t="n">
-        <v>1.3840830449827</v>
+        <v>9.98487140695915</v>
       </c>
       <c r="D588" t="b">
         <v>0</v>
@@ -10709,10 +10710,10 @@
         <v>591</v>
       </c>
       <c r="B589" t="n">
-        <v>20.611365319001</v>
+        <v>40.2826358390963</v>
       </c>
       <c r="C589" t="n">
-        <v>9.98487140695915</v>
+        <v>9.1358024691358</v>
       </c>
       <c r="D589" t="b">
         <v>0</v>
@@ -10723,10 +10724,10 @@
         <v>592</v>
       </c>
       <c r="B590" t="n">
-        <v>40.2826358390963</v>
+        <v>5.24544600992614</v>
       </c>
       <c r="C590" t="n">
-        <v>9.1358024691358</v>
+        <v>0</v>
       </c>
       <c r="D590" t="b">
         <v>0</v>
@@ -10737,13 +10738,13 @@
         <v>593</v>
       </c>
       <c r="B591" t="n">
-        <v>5.24544600992614</v>
+        <v>87.2902405910985</v>
       </c>
       <c r="C591" t="n">
-        <v>0</v>
+        <v>73.7373737373737</v>
       </c>
       <c r="D591" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="592">
@@ -10751,10 +10752,10 @@
         <v>594</v>
       </c>
       <c r="B592" t="n">
-        <v>87.2902405910985</v>
+        <v>99.9999999980029</v>
       </c>
       <c r="C592" t="n">
-        <v>73.7373737373737</v>
+        <v>100</v>
       </c>
       <c r="D592" t="b">
         <v>1</v>
@@ -10765,13 +10766,13 @@
         <v>595</v>
       </c>
       <c r="B593" t="n">
-        <v>99.9999999980029</v>
+        <v>5.51118928358048</v>
       </c>
       <c r="C593" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D593" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="594">
@@ -10779,7 +10780,7 @@
         <v>596</v>
       </c>
       <c r="B594" t="n">
-        <v>5.51118928358048</v>
+        <v>5.85426980412088</v>
       </c>
       <c r="C594" t="n">
         <v>0</v>
@@ -10793,10 +10794,10 @@
         <v>597</v>
       </c>
       <c r="B595" t="n">
-        <v>5.85426980412088</v>
+        <v>8.06256567559353</v>
       </c>
       <c r="C595" t="n">
-        <v>0</v>
+        <v>0.296296296296296</v>
       </c>
       <c r="D595" t="b">
         <v>0</v>
@@ -10807,10 +10808,10 @@
         <v>598</v>
       </c>
       <c r="B596" t="n">
-        <v>8.06256567559353</v>
+        <v>54.3159283237401</v>
       </c>
       <c r="C596" t="n">
-        <v>0.296296296296296</v>
+        <v>20.3208556149733</v>
       </c>
       <c r="D596" t="b">
         <v>0</v>
@@ -10821,10 +10822,10 @@
         <v>599</v>
       </c>
       <c r="B597" t="n">
-        <v>54.3159283237401</v>
+        <v>53.2559166610534</v>
       </c>
       <c r="C597" t="n">
-        <v>20.3208556149733</v>
+        <v>37.9032258064516</v>
       </c>
       <c r="D597" t="b">
         <v>0</v>
@@ -10835,10 +10836,10 @@
         <v>600</v>
       </c>
       <c r="B598" t="n">
-        <v>53.2559166610534</v>
+        <v>7.40944030337772</v>
       </c>
       <c r="C598" t="n">
-        <v>37.9032258064516</v>
+        <v>4.34782608695652</v>
       </c>
       <c r="D598" t="b">
         <v>0</v>
@@ -10849,10 +10850,10 @@
         <v>601</v>
       </c>
       <c r="B599" t="n">
-        <v>7.40944030337772</v>
+        <v>35.6019316791471</v>
       </c>
       <c r="C599" t="n">
-        <v>4.34782608695652</v>
+        <v>25.7731958762887</v>
       </c>
       <c r="D599" t="b">
         <v>0</v>
@@ -10863,13 +10864,13 @@
         <v>602</v>
       </c>
       <c r="B600" t="n">
-        <v>35.6019316791471</v>
+        <v>99.9999999999933</v>
       </c>
       <c r="C600" t="n">
-        <v>25.7731958762887</v>
+        <v>91.044776119403</v>
       </c>
       <c r="D600" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601">
@@ -10877,13 +10878,13 @@
         <v>603</v>
       </c>
       <c r="B601" t="n">
-        <v>99.9999999999933</v>
+        <v>65.0082812305675</v>
       </c>
       <c r="C601" t="n">
-        <v>91.044776119403</v>
+        <v>44.2857142857143</v>
       </c>
       <c r="D601" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="602">
@@ -10891,10 +10892,10 @@
         <v>604</v>
       </c>
       <c r="B602" t="n">
-        <v>65.0082812305675</v>
+        <v>60.5275762199573</v>
       </c>
       <c r="C602" t="n">
-        <v>44.2857142857143</v>
+        <v>35.4430379746835</v>
       </c>
       <c r="D602" t="b">
         <v>0</v>
@@ -10905,10 +10906,10 @@
         <v>605</v>
       </c>
       <c r="B603" t="n">
-        <v>60.5275762199573</v>
+        <v>5.55764334329572</v>
       </c>
       <c r="C603" t="n">
-        <v>35.4430379746835</v>
+        <v>0</v>
       </c>
       <c r="D603" t="b">
         <v>0</v>
@@ -10919,10 +10920,10 @@
         <v>606</v>
       </c>
       <c r="B604" t="n">
-        <v>5.55764334329572</v>
+        <v>10.0754979416774</v>
       </c>
       <c r="C604" t="n">
-        <v>0</v>
+        <v>3.27868852459016</v>
       </c>
       <c r="D604" t="b">
         <v>0</v>
@@ -10933,13 +10934,13 @@
         <v>607</v>
       </c>
       <c r="B605" t="n">
-        <v>10.0754979416774</v>
+        <v>84.0481170236581</v>
       </c>
       <c r="C605" t="n">
-        <v>3.27868852459016</v>
+        <v>56.25</v>
       </c>
       <c r="D605" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606">
@@ -10947,13 +10948,13 @@
         <v>608</v>
       </c>
       <c r="B606" t="n">
-        <v>84.0481170236581</v>
+        <v>27.338466456989</v>
       </c>
       <c r="C606" t="n">
-        <v>56.25</v>
+        <v>31.0810810810811</v>
       </c>
       <c r="D606" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="607">
@@ -10961,10 +10962,10 @@
         <v>609</v>
       </c>
       <c r="B607" t="n">
-        <v>27.338466456989</v>
+        <v>25.5756174902603</v>
       </c>
       <c r="C607" t="n">
-        <v>31.0810810810811</v>
+        <v>20.1834862385321</v>
       </c>
       <c r="D607" t="b">
         <v>0</v>
@@ -10975,10 +10976,10 @@
         <v>610</v>
       </c>
       <c r="B608" t="n">
-        <v>25.5756174902603</v>
+        <v>26.0201190380516</v>
       </c>
       <c r="C608" t="n">
-        <v>20.1834862385321</v>
+        <v>4.08163265306122</v>
       </c>
       <c r="D608" t="b">
         <v>0</v>
@@ -10989,10 +10990,10 @@
         <v>611</v>
       </c>
       <c r="B609" t="n">
-        <v>26.0201190380516</v>
+        <v>23.4517623271562</v>
       </c>
       <c r="C609" t="n">
-        <v>4.08163265306122</v>
+        <v>10.1694915254237</v>
       </c>
       <c r="D609" t="b">
         <v>0</v>
@@ -11003,13 +11004,13 @@
         <v>612</v>
       </c>
       <c r="B610" t="n">
-        <v>23.4517623271562</v>
+        <v>99.9971192010974</v>
       </c>
       <c r="C610" t="n">
-        <v>10.1694915254237</v>
+        <v>100</v>
       </c>
       <c r="D610" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611">
@@ -11017,10 +11018,10 @@
         <v>613</v>
       </c>
       <c r="B611" t="n">
-        <v>99.9971192010974</v>
+        <v>99.8806171237039</v>
       </c>
       <c r="C611" t="n">
-        <v>100</v>
+        <v>94.1176470588235</v>
       </c>
       <c r="D611" t="b">
         <v>1</v>
@@ -11031,10 +11032,10 @@
         <v>614</v>
       </c>
       <c r="B612" t="n">
-        <v>99.8806171237039</v>
+        <v>100</v>
       </c>
       <c r="C612" t="n">
-        <v>94.1176470588235</v>
+        <v>100</v>
       </c>
       <c r="D612" t="b">
         <v>1</v>
@@ -11045,13 +11046,13 @@
         <v>615</v>
       </c>
       <c r="B613" t="n">
-        <v>100</v>
+        <v>12.0595517228349</v>
       </c>
       <c r="C613" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D613" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -11059,7 +11060,7 @@
         <v>616</v>
       </c>
       <c r="B614" t="n">
-        <v>12.0595517228349</v>
+        <v>25.7294092141583</v>
       </c>
       <c r="C614" t="n">
         <v>0</v>
@@ -11073,10 +11074,10 @@
         <v>617</v>
       </c>
       <c r="B615" t="n">
-        <v>25.7294092141583</v>
+        <v>8.31794539355364</v>
       </c>
       <c r="C615" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D615" t="b">
         <v>0</v>
@@ -11087,13 +11088,13 @@
         <v>618</v>
       </c>
       <c r="B616" t="n">
-        <v>8.31794539355364</v>
+        <v>93.1563637103042</v>
       </c>
       <c r="C616" t="n">
-        <v>25</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="D616" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="617">
@@ -11101,13 +11102,13 @@
         <v>619</v>
       </c>
       <c r="B617" t="n">
-        <v>93.1563637103042</v>
+        <v>36.6070919495521</v>
       </c>
       <c r="C617" t="n">
-        <v>66.6666666666667</v>
+        <v>33.0578512396694</v>
       </c>
       <c r="D617" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="618">
@@ -11115,10 +11116,10 @@
         <v>620</v>
       </c>
       <c r="B618" t="n">
-        <v>36.6070919495521</v>
+        <v>5.50051379452378</v>
       </c>
       <c r="C618" t="n">
-        <v>33.0578512396694</v>
+        <v>0.65359477124183</v>
       </c>
       <c r="D618" t="b">
         <v>0</v>
@@ -11129,10 +11130,10 @@
         <v>621</v>
       </c>
       <c r="B619" t="n">
-        <v>5.50051379452378</v>
+        <v>19.4059788782786</v>
       </c>
       <c r="C619" t="n">
-        <v>0.65359477124183</v>
+        <v>13.3333333333333</v>
       </c>
       <c r="D619" t="b">
         <v>0</v>
@@ -11143,10 +11144,10 @@
         <v>622</v>
       </c>
       <c r="B620" t="n">
-        <v>19.4059788782786</v>
+        <v>5.58724117095102</v>
       </c>
       <c r="C620" t="n">
-        <v>13.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="D620" t="b">
         <v>0</v>
@@ -11157,10 +11158,10 @@
         <v>623</v>
       </c>
       <c r="B621" t="n">
-        <v>5.58724117095102</v>
+        <v>39.0366185654075</v>
       </c>
       <c r="C621" t="n">
-        <v>0</v>
+        <v>30.1369863013699</v>
       </c>
       <c r="D621" t="b">
         <v>0</v>
@@ -11171,10 +11172,10 @@
         <v>624</v>
       </c>
       <c r="B622" t="n">
-        <v>39.0366185654075</v>
+        <v>11.846598847468</v>
       </c>
       <c r="C622" t="n">
-        <v>30.1369863013699</v>
+        <v>0</v>
       </c>
       <c r="D622" t="b">
         <v>0</v>
@@ -11185,7 +11186,7 @@
         <v>625</v>
       </c>
       <c r="B623" t="n">
-        <v>11.846598847468</v>
+        <v>14.9289415226742</v>
       </c>
       <c r="C623" t="n">
         <v>0</v>
@@ -11199,7 +11200,7 @@
         <v>626</v>
       </c>
       <c r="B624" t="n">
-        <v>14.9289415226742</v>
+        <v>6.55834078220457</v>
       </c>
       <c r="C624" t="n">
         <v>0</v>
@@ -11213,7 +11214,7 @@
         <v>627</v>
       </c>
       <c r="B625" t="n">
-        <v>6.55834078220457</v>
+        <v>13.7524982018124</v>
       </c>
       <c r="C625" t="n">
         <v>0</v>
@@ -11227,10 +11228,10 @@
         <v>628</v>
       </c>
       <c r="B626" t="n">
-        <v>13.7524982018124</v>
+        <v>13.8790593781262</v>
       </c>
       <c r="C626" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D626" t="b">
         <v>0</v>
@@ -11241,10 +11242,10 @@
         <v>629</v>
       </c>
       <c r="B627" t="n">
-        <v>13.8790593781262</v>
+        <v>11.5581317728107</v>
       </c>
       <c r="C627" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D627" t="b">
         <v>0</v>
@@ -11255,7 +11256,7 @@
         <v>630</v>
       </c>
       <c r="B628" t="n">
-        <v>11.5581317728107</v>
+        <v>6.44637725973594</v>
       </c>
       <c r="C628" t="n">
         <v>0</v>
@@ -11269,7 +11270,7 @@
         <v>631</v>
       </c>
       <c r="B629" t="n">
-        <v>6.44637725973594</v>
+        <v>10.7922929746724</v>
       </c>
       <c r="C629" t="n">
         <v>0</v>
@@ -11283,7 +11284,7 @@
         <v>632</v>
       </c>
       <c r="B630" t="n">
-        <v>10.7922929746724</v>
+        <v>5.28306741797121</v>
       </c>
       <c r="C630" t="n">
         <v>0</v>
@@ -11297,7 +11298,7 @@
         <v>633</v>
       </c>
       <c r="B631" t="n">
-        <v>5.28306741797121</v>
+        <v>12.0892283606424</v>
       </c>
       <c r="C631" t="n">
         <v>0</v>
@@ -11311,7 +11312,7 @@
         <v>634</v>
       </c>
       <c r="B632" t="n">
-        <v>12.0892283606424</v>
+        <v>15.6187673978417</v>
       </c>
       <c r="C632" t="n">
         <v>0</v>
@@ -11325,7 +11326,7 @@
         <v>635</v>
       </c>
       <c r="B633" t="n">
-        <v>15.6187673978417</v>
+        <v>9.6642599822968</v>
       </c>
       <c r="C633" t="n">
         <v>0</v>
@@ -11339,7 +11340,7 @@
         <v>636</v>
       </c>
       <c r="B634" t="n">
-        <v>9.6642599822968</v>
+        <v>16.6441487525144</v>
       </c>
       <c r="C634" t="n">
         <v>0</v>
@@ -11353,7 +11354,7 @@
         <v>637</v>
       </c>
       <c r="B635" t="n">
-        <v>16.6441487525144</v>
+        <v>5.00043245757104</v>
       </c>
       <c r="C635" t="n">
         <v>0</v>
@@ -11367,10 +11368,10 @@
         <v>638</v>
       </c>
       <c r="B636" t="n">
-        <v>5.00043245757104</v>
+        <v>55.8162476743483</v>
       </c>
       <c r="C636" t="n">
-        <v>0</v>
+        <v>14.2857142857143</v>
       </c>
       <c r="D636" t="b">
         <v>0</v>
@@ -11381,10 +11382,10 @@
         <v>639</v>
       </c>
       <c r="B637" t="n">
-        <v>55.8162476743483</v>
+        <v>13.631295176298</v>
       </c>
       <c r="C637" t="n">
-        <v>14.2857142857143</v>
+        <v>0</v>
       </c>
       <c r="D637" t="b">
         <v>0</v>
@@ -11395,10 +11396,10 @@
         <v>640</v>
       </c>
       <c r="B638" t="n">
-        <v>13.631295176298</v>
+        <v>47.8654908229586</v>
       </c>
       <c r="C638" t="n">
-        <v>0</v>
+        <v>14.2857142857143</v>
       </c>
       <c r="D638" t="b">
         <v>0</v>
@@ -11409,10 +11410,10 @@
         <v>641</v>
       </c>
       <c r="B639" t="n">
-        <v>47.8654908229586</v>
+        <v>6.87952138124349</v>
       </c>
       <c r="C639" t="n">
-        <v>14.2857142857143</v>
+        <v>0</v>
       </c>
       <c r="D639" t="b">
         <v>0</v>
@@ -11423,7 +11424,7 @@
         <v>642</v>
       </c>
       <c r="B640" t="n">
-        <v>6.87952138124349</v>
+        <v>8.5424272841356</v>
       </c>
       <c r="C640" t="n">
         <v>0</v>
@@ -11437,7 +11438,7 @@
         <v>643</v>
       </c>
       <c r="B641" t="n">
-        <v>8.5424272841356</v>
+        <v>19.6851282276721</v>
       </c>
       <c r="C641" t="n">
         <v>0</v>
@@ -11451,7 +11452,7 @@
         <v>644</v>
       </c>
       <c r="B642" t="n">
-        <v>19.6851282276721</v>
+        <v>45.1672289752116</v>
       </c>
       <c r="C642" t="n">
         <v>0</v>
@@ -11465,7 +11466,7 @@
         <v>645</v>
       </c>
       <c r="B643" t="n">
-        <v>45.1672289752116</v>
+        <v>7.86337555375253</v>
       </c>
       <c r="C643" t="n">
         <v>0</v>
@@ -11479,7 +11480,7 @@
         <v>646</v>
       </c>
       <c r="B644" t="n">
-        <v>7.86337555375253</v>
+        <v>23.5404252414969</v>
       </c>
       <c r="C644" t="n">
         <v>0</v>
@@ -11493,7 +11494,7 @@
         <v>647</v>
       </c>
       <c r="B645" t="n">
-        <v>23.5404252414969</v>
+        <v>22.8522148563282</v>
       </c>
       <c r="C645" t="n">
         <v>0</v>
@@ -11507,10 +11508,10 @@
         <v>648</v>
       </c>
       <c r="B646" t="n">
-        <v>22.8522148563282</v>
+        <v>16.4895908760949</v>
       </c>
       <c r="C646" t="n">
-        <v>0</v>
+        <v>10.7438016528926</v>
       </c>
       <c r="D646" t="b">
         <v>0</v>
@@ -11521,10 +11522,10 @@
         <v>649</v>
       </c>
       <c r="B647" t="n">
-        <v>16.4895908760949</v>
+        <v>20.519163446341</v>
       </c>
       <c r="C647" t="n">
-        <v>10.7438016528926</v>
+        <v>15.3846153846154</v>
       </c>
       <c r="D647" t="b">
         <v>0</v>
@@ -11535,10 +11536,10 @@
         <v>650</v>
       </c>
       <c r="B648" t="n">
-        <v>20.519163446341</v>
+        <v>10.3438160353725</v>
       </c>
       <c r="C648" t="n">
-        <v>15.3846153846154</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="D648" t="b">
         <v>0</v>
@@ -11549,10 +11550,10 @@
         <v>651</v>
       </c>
       <c r="B649" t="n">
-        <v>10.3438160353725</v>
+        <v>7.43496816306362</v>
       </c>
       <c r="C649" t="n">
-        <v>16.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="D649" t="b">
         <v>0</v>
@@ -11563,7 +11564,7 @@
         <v>652</v>
       </c>
       <c r="B650" t="n">
-        <v>7.43496816306362</v>
+        <v>15.3832522600416</v>
       </c>
       <c r="C650" t="n">
         <v>0</v>
@@ -11577,7 +11578,7 @@
         <v>653</v>
       </c>
       <c r="B651" t="n">
-        <v>15.3832522600416</v>
+        <v>35.8914068503174</v>
       </c>
       <c r="C651" t="n">
         <v>0</v>
@@ -11591,13 +11592,13 @@
         <v>654</v>
       </c>
       <c r="B652" t="n">
-        <v>35.8914068503174</v>
+        <v>87.9025311482832</v>
       </c>
       <c r="C652" t="n">
-        <v>0</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="D652" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="653">
@@ -11605,13 +11606,13 @@
         <v>655</v>
       </c>
       <c r="B653" t="n">
-        <v>87.9025311482832</v>
+        <v>56.435251289419</v>
       </c>
       <c r="C653" t="n">
-        <v>57.1428571428571</v>
+        <v>8.7378640776699</v>
       </c>
       <c r="D653" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="654">
@@ -11619,10 +11620,10 @@
         <v>656</v>
       </c>
       <c r="B654" t="n">
-        <v>56.435251289419</v>
+        <v>5.46253221057518</v>
       </c>
       <c r="C654" t="n">
-        <v>8.7378640776699</v>
+        <v>0</v>
       </c>
       <c r="D654" t="b">
         <v>0</v>
@@ -11633,10 +11634,10 @@
         <v>657</v>
       </c>
       <c r="B655" t="n">
-        <v>5.46253221057518</v>
+        <v>10.5116542683403</v>
       </c>
       <c r="C655" t="n">
-        <v>0</v>
+        <v>6.45161290322581</v>
       </c>
       <c r="D655" t="b">
         <v>0</v>
@@ -11647,10 +11648,10 @@
         <v>658</v>
       </c>
       <c r="B656" t="n">
-        <v>10.5116542683403</v>
+        <v>8.19175418317443</v>
       </c>
       <c r="C656" t="n">
-        <v>6.45161290322581</v>
+        <v>1.69491525423729</v>
       </c>
       <c r="D656" t="b">
         <v>0</v>
@@ -11661,10 +11662,10 @@
         <v>659</v>
       </c>
       <c r="B657" t="n">
-        <v>8.19175418317443</v>
+        <v>6.6412328383236</v>
       </c>
       <c r="C657" t="n">
-        <v>1.69491525423729</v>
+        <v>0</v>
       </c>
       <c r="D657" t="b">
         <v>0</v>
@@ -11675,7 +11676,7 @@
         <v>660</v>
       </c>
       <c r="B658" t="n">
-        <v>6.6412328383236</v>
+        <v>8.07179369696773</v>
       </c>
       <c r="C658" t="n">
         <v>0</v>
@@ -11689,10 +11690,10 @@
         <v>661</v>
       </c>
       <c r="B659" t="n">
-        <v>8.07179369696773</v>
+        <v>53.5026899163475</v>
       </c>
       <c r="C659" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="D659" t="b">
         <v>0</v>
@@ -11703,10 +11704,10 @@
         <v>662</v>
       </c>
       <c r="B660" t="n">
-        <v>53.5026899163475</v>
+        <v>15.5409568327678</v>
       </c>
       <c r="C660" t="n">
-        <v>16.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="D660" t="b">
         <v>0</v>
@@ -11717,10 +11718,10 @@
         <v>663</v>
       </c>
       <c r="B661" t="n">
-        <v>15.5409568327678</v>
+        <v>23.2169180644919</v>
       </c>
       <c r="C661" t="n">
-        <v>0</v>
+        <v>14.2857142857143</v>
       </c>
       <c r="D661" t="b">
         <v>0</v>
@@ -11731,10 +11732,10 @@
         <v>664</v>
       </c>
       <c r="B662" t="n">
-        <v>23.2169180644919</v>
+        <v>5.05228137677442</v>
       </c>
       <c r="C662" t="n">
-        <v>14.2857142857143</v>
+        <v>0</v>
       </c>
       <c r="D662" t="b">
         <v>0</v>
@@ -11745,13 +11746,13 @@
         <v>665</v>
       </c>
       <c r="B663" t="n">
-        <v>5.05228137677442</v>
+        <v>91.8060633331804</v>
       </c>
       <c r="C663" t="n">
-        <v>0</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="D663" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="664">
@@ -11759,10 +11760,10 @@
         <v>666</v>
       </c>
       <c r="B664" t="n">
-        <v>91.8060633331804</v>
+        <v>99.9981419505069</v>
       </c>
       <c r="C664" t="n">
-        <v>71.4285714285714</v>
+        <v>87.5</v>
       </c>
       <c r="D664" t="b">
         <v>1</v>
@@ -11773,13 +11774,13 @@
         <v>667</v>
       </c>
       <c r="B665" t="n">
-        <v>99.9981419505069</v>
+        <v>51.0757682244186</v>
       </c>
       <c r="C665" t="n">
-        <v>87.5</v>
+        <v>16.1290322580645</v>
       </c>
       <c r="D665" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="666">
@@ -11787,10 +11788,10 @@
         <v>668</v>
       </c>
       <c r="B666" t="n">
-        <v>51.0757682244186</v>
+        <v>5.01141978526531</v>
       </c>
       <c r="C666" t="n">
-        <v>16.1290322580645</v>
+        <v>0</v>
       </c>
       <c r="D666" t="b">
         <v>0</v>
@@ -11801,10 +11802,10 @@
         <v>669</v>
       </c>
       <c r="B667" t="n">
-        <v>5.01141978526531</v>
+        <v>17.0613264327695</v>
       </c>
       <c r="C667" t="n">
-        <v>0</v>
+        <v>26.6666666666667</v>
       </c>
       <c r="D667" t="b">
         <v>0</v>
@@ -11815,13 +11816,13 @@
         <v>670</v>
       </c>
       <c r="B668" t="n">
-        <v>17.0613264327695</v>
+        <v>82.8775050302129</v>
       </c>
       <c r="C668" t="n">
-        <v>26.6666666666667</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="D668" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
@@ -11829,13 +11830,13 @@
         <v>671</v>
       </c>
       <c r="B669" t="n">
-        <v>82.8775050302129</v>
+        <v>5.08229478050488</v>
       </c>
       <c r="C669" t="n">
-        <v>57.1428571428571</v>
+        <v>0</v>
       </c>
       <c r="D669" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="670">
@@ -11843,13 +11844,13 @@
         <v>672</v>
       </c>
       <c r="B670" t="n">
-        <v>5.08229478050488</v>
+        <v>92.9104041023695</v>
       </c>
       <c r="C670" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D670" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671">
@@ -11857,13 +11858,13 @@
         <v>673</v>
       </c>
       <c r="B671" t="n">
-        <v>92.9104041023695</v>
+        <v>5.79845530722079</v>
       </c>
       <c r="C671" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D671" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="672">
@@ -11871,7 +11872,7 @@
         <v>674</v>
       </c>
       <c r="B672" t="n">
-        <v>5.79845530722079</v>
+        <v>7.47536755153435</v>
       </c>
       <c r="C672" t="n">
         <v>0</v>
@@ -11885,7 +11886,7 @@
         <v>675</v>
       </c>
       <c r="B673" t="n">
-        <v>7.47536755153435</v>
+        <v>25.0452511469619</v>
       </c>
       <c r="C673" t="n">
         <v>0</v>
@@ -11899,7 +11900,7 @@
         <v>676</v>
       </c>
       <c r="B674" t="n">
-        <v>25.0452511469619</v>
+        <v>5.00025681926845</v>
       </c>
       <c r="C674" t="n">
         <v>0</v>
@@ -11913,10 +11914,10 @@
         <v>677</v>
       </c>
       <c r="B675" t="n">
-        <v>5.00025681926845</v>
+        <v>33.5205165144263</v>
       </c>
       <c r="C675" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D675" t="b">
         <v>0</v>
@@ -11927,10 +11928,10 @@
         <v>678</v>
       </c>
       <c r="B676" t="n">
-        <v>33.5205165144263</v>
+        <v>5.0159814175221</v>
       </c>
       <c r="C676" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D676" t="b">
         <v>0</v>
@@ -11941,7 +11942,7 @@
         <v>679</v>
       </c>
       <c r="B677" t="n">
-        <v>5.0159814175221</v>
+        <v>6.89109915616534</v>
       </c>
       <c r="C677" t="n">
         <v>0</v>
@@ -11955,7 +11956,7 @@
         <v>680</v>
       </c>
       <c r="B678" t="n">
-        <v>6.89109915616534</v>
+        <v>5.02448726436799</v>
       </c>
       <c r="C678" t="n">
         <v>0</v>
@@ -11969,7 +11970,7 @@
         <v>681</v>
       </c>
       <c r="B679" t="n">
-        <v>5.02448726436799</v>
+        <v>61.9045336932341</v>
       </c>
       <c r="C679" t="n">
         <v>0</v>
@@ -11983,13 +11984,13 @@
         <v>682</v>
       </c>
       <c r="B680" t="n">
-        <v>61.9045336932341</v>
+        <v>100</v>
       </c>
       <c r="C680" t="n">
-        <v>0</v>
+        <v>80.7692307692308</v>
       </c>
       <c r="D680" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681">
@@ -12000,7 +12001,7 @@
         <v>100</v>
       </c>
       <c r="C681" t="n">
-        <v>80.7692307692308</v>
+        <v>73.134328358209</v>
       </c>
       <c r="D681" t="b">
         <v>1</v>
@@ -12014,7 +12015,7 @@
         <v>100</v>
       </c>
       <c r="C682" t="n">
-        <v>73.134328358209</v>
+        <v>98.3455882352941</v>
       </c>
       <c r="D682" t="b">
         <v>1</v>
@@ -12028,7 +12029,7 @@
         <v>100</v>
       </c>
       <c r="C683" t="n">
-        <v>98.3455882352941</v>
+        <v>87.0967741935484</v>
       </c>
       <c r="D683" t="b">
         <v>1</v>
@@ -12042,7 +12043,7 @@
         <v>100</v>
       </c>
       <c r="C684" t="n">
-        <v>87.0967741935484</v>
+        <v>88.4615384615385</v>
       </c>
       <c r="D684" t="b">
         <v>1</v>
@@ -12056,7 +12057,7 @@
         <v>100</v>
       </c>
       <c r="C685" t="n">
-        <v>88.4615384615385</v>
+        <v>92.3664122137405</v>
       </c>
       <c r="D685" t="b">
         <v>1</v>
@@ -12070,7 +12071,7 @@
         <v>100</v>
       </c>
       <c r="C686" t="n">
-        <v>92.3664122137405</v>
+        <v>93.4210526315789</v>
       </c>
       <c r="D686" t="b">
         <v>1</v>
@@ -12084,7 +12085,7 @@
         <v>100</v>
       </c>
       <c r="C687" t="n">
-        <v>93.4210526315789</v>
+        <v>82.7777777777778</v>
       </c>
       <c r="D687" t="b">
         <v>1</v>
@@ -12098,7 +12099,7 @@
         <v>100</v>
       </c>
       <c r="C688" t="n">
-        <v>82.7777777777778</v>
+        <v>94.8680351906158</v>
       </c>
       <c r="D688" t="b">
         <v>1</v>
@@ -12112,7 +12113,7 @@
         <v>100</v>
       </c>
       <c r="C689" t="n">
-        <v>94.8680351906158</v>
+        <v>100</v>
       </c>
       <c r="D689" t="b">
         <v>1</v>
@@ -12126,7 +12127,7 @@
         <v>100</v>
       </c>
       <c r="C690" t="n">
-        <v>100</v>
+        <v>79.0697674418605</v>
       </c>
       <c r="D690" t="b">
         <v>1</v>
@@ -12140,7 +12141,7 @@
         <v>100</v>
       </c>
       <c r="C691" t="n">
-        <v>79.0697674418605</v>
+        <v>100</v>
       </c>
       <c r="D691" t="b">
         <v>1</v>
@@ -12151,13 +12152,13 @@
         <v>694</v>
       </c>
       <c r="B692" t="n">
-        <v>100</v>
+        <v>77.3744985120217</v>
       </c>
       <c r="C692" t="n">
-        <v>100</v>
+        <v>49.2307692307692</v>
       </c>
       <c r="D692" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693">
@@ -12165,13 +12166,13 @@
         <v>695</v>
       </c>
       <c r="B693" t="n">
-        <v>77.3744985120217</v>
+        <v>99.824382253234</v>
       </c>
       <c r="C693" t="n">
-        <v>49.2307692307692</v>
+        <v>77.2277227722772</v>
       </c>
       <c r="D693" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694">
@@ -12179,13 +12180,13 @@
         <v>696</v>
       </c>
       <c r="B694" t="n">
-        <v>99.824382253234</v>
+        <v>5.114182130714</v>
       </c>
       <c r="C694" t="n">
-        <v>77.2277227722772</v>
+        <v>0</v>
       </c>
       <c r="D694" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="695">
@@ -12193,10 +12194,10 @@
         <v>697</v>
       </c>
       <c r="B695" t="n">
-        <v>5.114182130714</v>
+        <v>5.57238530166088</v>
       </c>
       <c r="C695" t="n">
-        <v>0</v>
+        <v>4.08163265306122</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -12207,10 +12208,10 @@
         <v>698</v>
       </c>
       <c r="B696" t="n">
-        <v>5.57238530166088</v>
+        <v>10.7898222079201</v>
       </c>
       <c r="C696" t="n">
-        <v>4.08163265306122</v>
+        <v>0</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -12221,7 +12222,7 @@
         <v>699</v>
       </c>
       <c r="B697" t="n">
-        <v>10.7898222079201</v>
+        <v>8.75244940153972</v>
       </c>
       <c r="C697" t="n">
         <v>0</v>
@@ -12235,7 +12236,7 @@
         <v>700</v>
       </c>
       <c r="B698" t="n">
-        <v>8.75244940153972</v>
+        <v>5.22802076835081</v>
       </c>
       <c r="C698" t="n">
         <v>0</v>
@@ -12249,10 +12250,10 @@
         <v>701</v>
       </c>
       <c r="B699" t="n">
-        <v>5.22802076835081</v>
+        <v>47.9380968951652</v>
       </c>
       <c r="C699" t="n">
-        <v>0</v>
+        <v>30.7692307692308</v>
       </c>
       <c r="D699" t="b">
         <v>0</v>
@@ -12263,10 +12264,10 @@
         <v>702</v>
       </c>
       <c r="B700" t="n">
-        <v>47.9380968951652</v>
+        <v>23.0117663997403</v>
       </c>
       <c r="C700" t="n">
-        <v>30.7692307692308</v>
+        <v>12.5</v>
       </c>
       <c r="D700" t="b">
         <v>0</v>
@@ -12277,10 +12278,10 @@
         <v>703</v>
       </c>
       <c r="B701" t="n">
-        <v>23.0117663997403</v>
+        <v>36.3869438027054</v>
       </c>
       <c r="C701" t="n">
-        <v>12.5</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="D701" t="b">
         <v>0</v>
@@ -12291,10 +12292,10 @@
         <v>704</v>
       </c>
       <c r="B702" t="n">
-        <v>36.3869438027054</v>
+        <v>5.36527646977927</v>
       </c>
       <c r="C702" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="D702" t="b">
         <v>0</v>
@@ -12305,10 +12306,10 @@
         <v>705</v>
       </c>
       <c r="B703" t="n">
-        <v>5.36527646977927</v>
+        <v>74.4259184928191</v>
       </c>
       <c r="C703" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D703" t="b">
         <v>0</v>
@@ -12319,10 +12320,10 @@
         <v>706</v>
       </c>
       <c r="B704" t="n">
-        <v>74.4259184928191</v>
+        <v>42.0690695104715</v>
       </c>
       <c r="C704" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D704" t="b">
         <v>0</v>
@@ -12333,10 +12334,10 @@
         <v>707</v>
       </c>
       <c r="B705" t="n">
-        <v>42.0690695104715</v>
+        <v>13.8630897787221</v>
       </c>
       <c r="C705" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D705" t="b">
         <v>0</v>
@@ -12347,7 +12348,7 @@
         <v>708</v>
       </c>
       <c r="B706" t="n">
-        <v>13.8630897787221</v>
+        <v>46.0180813740649</v>
       </c>
       <c r="C706" t="n">
         <v>0</v>
@@ -12361,7 +12362,7 @@
         <v>709</v>
       </c>
       <c r="B707" t="n">
-        <v>46.0180813740649</v>
+        <v>5.94727414683899</v>
       </c>
       <c r="C707" t="n">
         <v>0</v>
@@ -12375,26 +12376,12 @@
         <v>710</v>
       </c>
       <c r="B708" t="n">
-        <v>5.94727414683899</v>
+        <v>5.74383765151481</v>
       </c>
       <c r="C708" t="n">
         <v>0</v>
       </c>
       <c r="D708" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="s">
-        <v>711</v>
-      </c>
-      <c r="B709" t="n">
-        <v>5.74383765151481</v>
-      </c>
-      <c r="C709" t="n">
-        <v>0</v>
-      </c>
-      <c r="D709" t="b">
         <v>0</v>
       </c>
     </row>
